--- a/File Templates/League Multipliers.xlsx
+++ b/File Templates/League Multipliers.xlsx
@@ -1,33 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Client\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\FM24-Filter_JG\File Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0697E617-150D-4FF6-B4BD-A6E4D9C25086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1AC2E2-1F6C-4120-93EB-AFAA8303DBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F58F6362-BB4A-47F5-A614-880E00C06A59}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$273</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -862,7 +856,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -883,6 +877,12 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -898,7 +898,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -921,17 +921,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1266,7 +1284,7 @@
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>100</v>
       </c>
     </row>
@@ -1274,527 +1292,527 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>99</v>
+      <c r="B3" s="3">
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>98</v>
+      <c r="B4" s="3">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>97</v>
+      <c r="B5" s="3">
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>96</v>
+      <c r="B6" s="3">
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>92</v>
+      <c r="B7" s="3">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>91</v>
+      <c r="B8" s="3">
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>90</v>
+      <c r="B9" s="3">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>88</v>
+      <c r="B10" s="3">
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>87</v>
+      <c r="B11" s="3">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>86</v>
+      <c r="B12" s="3">
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13">
-        <v>85</v>
+      <c r="B13" s="3">
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14">
-        <v>84</v>
+      <c r="B14" s="3">
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>83</v>
+      <c r="B15" s="3">
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16">
-        <v>82</v>
+      <c r="B16" s="3">
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17">
-        <v>81</v>
+      <c r="B17" s="3">
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B18">
-        <v>80</v>
+      <c r="B18" s="3">
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B19">
-        <v>79</v>
+      <c r="B19" s="3">
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B20">
-        <v>78</v>
+      <c r="B20" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B21">
-        <v>77</v>
+      <c r="B21" s="3">
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22">
-        <v>76</v>
+      <c r="B22" s="3">
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23">
-        <v>75</v>
+      <c r="B23" s="3">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B24">
-        <v>74</v>
+      <c r="B24" s="3">
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B25">
-        <v>73</v>
+      <c r="B25" s="3">
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B26">
-        <v>72</v>
+      <c r="B26" s="3">
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27">
-        <v>71</v>
+      <c r="B27" s="3">
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B28">
-        <v>70</v>
+      <c r="B28" s="3">
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B29">
-        <v>69</v>
+      <c r="B29" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B30">
-        <v>68</v>
+      <c r="B30" s="3">
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B31">
-        <v>67</v>
+      <c r="B31" s="3">
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B32">
-        <v>66</v>
+      <c r="B32" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B33">
-        <v>65</v>
+      <c r="B33" s="3">
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B34">
-        <v>64</v>
+      <c r="B34" s="3">
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B35">
-        <v>63</v>
+      <c r="B35" s="3">
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B36">
-        <v>62</v>
+      <c r="B36" s="3">
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B37">
-        <v>61</v>
+      <c r="B37" s="3">
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B38">
-        <v>60</v>
+      <c r="B38" s="3">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B39">
-        <v>59</v>
+      <c r="B39" s="3">
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B40">
-        <v>58</v>
+      <c r="B40" s="3">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B41">
-        <v>57</v>
+      <c r="B41" s="3">
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B42">
-        <v>56</v>
+      <c r="B42" s="3">
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B43">
-        <v>55</v>
+      <c r="B43" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B44">
-        <v>54</v>
+      <c r="B44" s="3">
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B45">
-        <v>53</v>
+      <c r="B45" s="3">
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B46">
-        <v>52</v>
+      <c r="B46" s="3">
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B47">
-        <v>51</v>
+      <c r="B47" s="3">
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B48">
-        <v>50</v>
+      <c r="B48" s="3">
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B49">
-        <v>49</v>
+      <c r="B49" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B50">
-        <v>48</v>
+      <c r="B50" s="3">
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B51">
-        <v>47</v>
+      <c r="B51" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B52">
-        <v>46</v>
+      <c r="B52" s="3">
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B53">
-        <v>45</v>
+      <c r="B53" s="3">
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B54">
-        <v>44</v>
+      <c r="B54" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B55">
-        <v>43</v>
+      <c r="B55" s="3">
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B56">
-        <v>42</v>
+      <c r="B56" s="3">
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B57">
-        <v>41</v>
+      <c r="B57" s="3">
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B58">
-        <v>40</v>
+      <c r="B58" s="3">
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B59">
-        <v>39</v>
+      <c r="B59" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B60">
-        <v>38</v>
+      <c r="B60" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B61">
-        <v>37</v>
+      <c r="B61" s="3">
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B62">
-        <v>36</v>
+      <c r="B62" s="3">
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B63">
-        <v>35</v>
+      <c r="B63" s="3">
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B64">
-        <v>34</v>
+      <c r="B64" s="3">
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B65">
-        <v>33</v>
+      <c r="B65" s="3">
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B66">
-        <v>32</v>
+      <c r="B66" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B67">
-        <v>31</v>
+      <c r="B67" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="3">
         <v>30</v>
       </c>
     </row>
@@ -1802,47 +1820,47 @@
       <c r="A69" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B69">
-        <v>29</v>
+      <c r="B69" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B70">
-        <v>28</v>
+      <c r="B70" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B71">
-        <v>27</v>
+      <c r="B71" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B72">
-        <v>26</v>
+      <c r="B72" s="3">
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B73">
-        <v>25</v>
+      <c r="B73" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="3">
         <v>24</v>
       </c>
     </row>
@@ -1850,607 +1868,607 @@
       <c r="A75" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B75">
-        <v>23</v>
+      <c r="B75" s="3">
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B76">
-        <v>22</v>
+      <c r="B76" s="3">
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B77">
-        <v>21</v>
+      <c r="B77" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B78">
-        <v>20</v>
+      <c r="B78" s="3">
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B79">
-        <v>19</v>
+      <c r="B79" s="3">
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B80">
-        <v>18</v>
+      <c r="B80" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B81">
-        <v>17</v>
+      <c r="B81" s="3">
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B82">
-        <v>16</v>
+      <c r="B82" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B83">
-        <v>15</v>
+      <c r="B83" s="3">
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B84">
-        <v>14</v>
+      <c r="B84" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B85">
-        <v>13</v>
+      <c r="B85" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B86">
-        <v>12</v>
+      <c r="B86" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B87">
-        <v>11</v>
+      <c r="B87" s="3">
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B88">
-        <v>10</v>
+      <c r="B88" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B89">
-        <v>9</v>
+      <c r="B89" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B90">
-        <v>8</v>
+      <c r="B90" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B91">
-        <v>7</v>
+      <c r="B91" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B92">
-        <v>6</v>
+      <c r="B92" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B93">
-        <v>5</v>
+      <c r="B93" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B94">
-        <v>4</v>
+      <c r="B94" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B95">
-        <v>3</v>
+      <c r="B95" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B96">
-        <v>2</v>
+      <c r="B96" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B97">
-        <v>2</v>
+      <c r="B97" s="3">
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B98">
-        <v>2</v>
+      <c r="B98" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B99">
-        <v>2</v>
+      <c r="B99" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B100">
-        <v>2</v>
+      <c r="B100" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B101">
-        <v>2</v>
+      <c r="B101" s="3">
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B102">
-        <v>2</v>
+      <c r="B102" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B103">
-        <v>2</v>
+      <c r="B103" s="3">
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B104">
-        <v>2</v>
+      <c r="B104" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B105">
-        <v>2</v>
+      <c r="B105" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B106">
-        <v>2</v>
+      <c r="B106" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B107">
-        <v>2</v>
+      <c r="B107" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B108">
-        <v>2</v>
+      <c r="B108" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B109">
-        <v>2</v>
+      <c r="B109" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B110">
-        <v>2</v>
+      <c r="B110" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B111">
-        <v>2</v>
+      <c r="B111" s="3">
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B112">
-        <v>2</v>
+      <c r="B112" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B113">
-        <v>2</v>
+      <c r="B113" s="3">
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B114">
-        <v>2</v>
+      <c r="B114" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B115">
-        <v>2</v>
+      <c r="B115" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B116">
-        <v>2</v>
+      <c r="B116" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B117">
-        <v>2</v>
+      <c r="B117" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B118">
-        <v>2</v>
+      <c r="B118" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B119">
-        <v>2</v>
+      <c r="B119" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B120">
-        <v>2</v>
+      <c r="B120" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B121">
-        <v>2</v>
+      <c r="B121" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B122">
-        <v>2</v>
+      <c r="B122" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B123">
-        <v>2</v>
+      <c r="B123" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B124">
-        <v>2</v>
+      <c r="B124" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B125">
-        <v>2</v>
+      <c r="B125" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B126">
-        <v>2</v>
+      <c r="B126" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B127">
-        <v>2</v>
+      <c r="B127" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B128">
-        <v>2</v>
+      <c r="B128" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B129">
-        <v>2</v>
+      <c r="B129" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B130">
-        <v>2</v>
+      <c r="B130" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B131">
-        <v>2</v>
+      <c r="B131" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B132">
-        <v>2</v>
+      <c r="B132" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B133">
-        <v>1</v>
+      <c r="B133" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B134">
-        <v>1</v>
+      <c r="B134" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B135">
-        <v>1</v>
+      <c r="B135" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B136">
-        <v>1</v>
+      <c r="B136" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B137">
-        <v>1</v>
+      <c r="B137" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B138">
-        <v>1</v>
+      <c r="B138" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B139">
-        <v>1</v>
+      <c r="B139" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B140">
-        <v>1</v>
+      <c r="B140" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B141">
-        <v>1</v>
+      <c r="B141" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B142">
-        <v>1</v>
+      <c r="B142" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B143">
-        <v>1</v>
+      <c r="B143" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B144">
-        <v>1</v>
+      <c r="B144" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B145">
-        <v>1</v>
+      <c r="B145" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B146">
-        <v>1</v>
+      <c r="B146" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B147">
-        <v>1</v>
+      <c r="B147" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B148">
-        <v>1</v>
+      <c r="B148" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B149">
-        <v>1</v>
+      <c r="B149" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2458,887 +2476,887 @@
       <c r="A151" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B151">
-        <v>1</v>
+      <c r="B151" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B152">
-        <v>1</v>
+      <c r="B152" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B153">
-        <v>1</v>
+      <c r="B153" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B154">
-        <v>1</v>
+      <c r="B154" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B155">
-        <v>1</v>
+      <c r="B155" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B156">
-        <v>1</v>
+      <c r="B156" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B157">
-        <v>1</v>
+      <c r="B157" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B158">
-        <v>1</v>
+      <c r="B158" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B159">
-        <v>1</v>
+      <c r="B159" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B160">
-        <v>1</v>
+      <c r="B160" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B161">
-        <v>1</v>
+      <c r="B161" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B162">
-        <v>1</v>
+      <c r="B162" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B163">
-        <v>1</v>
+      <c r="B163" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B164">
-        <v>1</v>
+      <c r="B164" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B165">
-        <v>1</v>
+      <c r="B165" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B166">
-        <v>1</v>
+      <c r="B166" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B167">
-        <v>1</v>
+      <c r="B167" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B168">
-        <v>1</v>
+      <c r="B168" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B169">
-        <v>1</v>
+      <c r="B169" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B170">
-        <v>1</v>
+      <c r="B170" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B171">
-        <v>1</v>
+      <c r="B171" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B172">
-        <v>1</v>
+      <c r="B172" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B173">
-        <v>1</v>
+      <c r="B173" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B174">
-        <v>1</v>
+      <c r="B174" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B175">
-        <v>1</v>
+      <c r="B175" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B176">
-        <v>1</v>
+      <c r="B176" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B177">
-        <v>1</v>
+      <c r="B177" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B178">
-        <v>1</v>
+      <c r="B178" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B179">
-        <v>1</v>
+      <c r="B179" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B180">
-        <v>1</v>
+      <c r="B180" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B181">
-        <v>1</v>
+      <c r="B181" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B182">
-        <v>1</v>
+      <c r="B182" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B183">
-        <v>1</v>
+      <c r="B183" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B184">
-        <v>1</v>
+      <c r="B184" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B185">
-        <v>1</v>
+      <c r="B185" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B186">
-        <v>1</v>
+      <c r="B186" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B187">
-        <v>1</v>
+      <c r="B187" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B188">
-        <v>1</v>
+      <c r="B188" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B189">
-        <v>1</v>
+      <c r="B189" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B190">
-        <v>1</v>
+      <c r="B190" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B191">
-        <v>1</v>
+      <c r="B191" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B192">
-        <v>1</v>
+      <c r="B192" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B193">
-        <v>1</v>
+      <c r="B193" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B194">
-        <v>1</v>
+      <c r="B194" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B195">
-        <v>1</v>
+      <c r="B195" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B196">
-        <v>1</v>
+      <c r="B196" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B197">
-        <v>1</v>
+      <c r="B197" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B198">
-        <v>1</v>
+      <c r="B198" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B199">
-        <v>1</v>
+      <c r="B199" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B200">
-        <v>1</v>
+      <c r="B200" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B201">
-        <v>1</v>
+      <c r="B201" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B202">
-        <v>1</v>
+      <c r="B202" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B203">
-        <v>1</v>
+      <c r="B203" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B204">
-        <v>1</v>
+      <c r="B204" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B205">
-        <v>1</v>
+      <c r="B205" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B206">
-        <v>1</v>
+      <c r="B206" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B207">
-        <v>1</v>
+      <c r="B207" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B208">
-        <v>1</v>
+      <c r="B208" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B209">
-        <v>1</v>
+      <c r="B209" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B210">
-        <v>1</v>
+      <c r="B210" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B211">
-        <v>1</v>
+      <c r="B211" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B212">
-        <v>1</v>
+      <c r="B212" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B213">
-        <v>1</v>
+      <c r="B213" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B214">
-        <v>1</v>
+      <c r="B214" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B215">
-        <v>1</v>
+      <c r="B215" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B216">
-        <v>1</v>
+      <c r="B216" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B217">
-        <v>1</v>
+      <c r="B217" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B218">
-        <v>1</v>
+      <c r="B218" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B219">
-        <v>1</v>
+      <c r="B219" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B220">
-        <v>1</v>
+      <c r="B220" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B221">
-        <v>1</v>
+      <c r="B221" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B222">
-        <v>1</v>
+      <c r="B222" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B223">
-        <v>1</v>
+      <c r="B223" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B224">
-        <v>1</v>
+      <c r="B224" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B225">
-        <v>1</v>
+      <c r="B225" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B226">
-        <v>1</v>
+      <c r="B226" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B227">
-        <v>1</v>
+      <c r="B227" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B228">
-        <v>1</v>
+      <c r="B228" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B229">
-        <v>1</v>
+      <c r="B229" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B230">
-        <v>1</v>
+      <c r="B230" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B231">
-        <v>1</v>
+      <c r="B231" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B232">
-        <v>1</v>
+      <c r="B232" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B233">
-        <v>1</v>
+      <c r="B233" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B234">
-        <v>1</v>
+      <c r="B234" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B235">
-        <v>1</v>
+      <c r="B235" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B236">
-        <v>1</v>
+      <c r="B236" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B237">
-        <v>1</v>
+      <c r="B237" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B238">
-        <v>1</v>
+      <c r="B238" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B239">
-        <v>1</v>
+      <c r="B239" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B240">
-        <v>1</v>
+      <c r="B240" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B241">
-        <v>1</v>
+      <c r="B241" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B242">
-        <v>1</v>
+      <c r="B242" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B243">
-        <v>1</v>
+      <c r="B243" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B244">
-        <v>1</v>
+      <c r="B244" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B245">
-        <v>1</v>
+      <c r="B245" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B246">
-        <v>1</v>
+      <c r="B246" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B247">
-        <v>1</v>
+      <c r="B247" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B248">
-        <v>1</v>
+      <c r="B248" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B249">
-        <v>1</v>
+      <c r="B249" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B250">
-        <v>1</v>
+      <c r="B250" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B251">
-        <v>1</v>
+      <c r="B251" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B252">
-        <v>1</v>
+      <c r="B252" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B253">
-        <v>1</v>
+      <c r="B253" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B254">
-        <v>1</v>
+      <c r="B254" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B255">
-        <v>1</v>
+      <c r="B255" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B256">
-        <v>1</v>
+      <c r="B256" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B257">
-        <v>1</v>
+      <c r="B257" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B258">
-        <v>1</v>
+      <c r="B258" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B259">
-        <v>1</v>
+      <c r="B259" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B260">
-        <v>1</v>
+      <c r="B260" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="3">
         <v>1</v>
       </c>
     </row>
@@ -3346,102 +3364,103 @@
       <c r="A262" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B262">
-        <v>1</v>
+      <c r="B262" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B263">
-        <v>1</v>
+      <c r="B263" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B264">
-        <v>1</v>
+      <c r="B264" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B265">
-        <v>1</v>
+      <c r="B265" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B266">
-        <v>1</v>
+      <c r="B266" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B267">
-        <v>1</v>
+      <c r="B267" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B268">
-        <v>1</v>
+      <c r="B268" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B269">
-        <v>1</v>
+      <c r="B269" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B270">
-        <v>1</v>
+      <c r="B270" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B271">
-        <v>1</v>
+      <c r="B271" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B272">
-        <v>1</v>
+      <c r="B272" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B273">
-        <v>1</v>
+      <c r="B273" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C273" xr:uid="{8C43EA2F-F7A9-497C-AA9A-8BD0FB3A104B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/File Templates/League Multipliers.xlsx
+++ b/File Templates/League Multipliers.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20375"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\FM24-Filter_JG\File Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Sports Interactive\Football Manager 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1AC2E2-1F6C-4120-93EB-AFAA8303DBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9501EF2-17DB-4BE7-A35A-028051D7F117}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F58F6362-BB4A-47F5-A614-880E00C06A59}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$273</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -877,12 +877,6 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -898,7 +892,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -921,35 +915,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1284,7 +1260,7 @@
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>100</v>
       </c>
     </row>
@@ -1292,2168 +1268,2168 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>94</v>
+      <c r="B3">
+        <v>99.744245524296673</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
-        <v>92</v>
+      <c r="B4">
+        <v>99.488491048593346</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
-        <v>91</v>
+      <c r="B5">
+        <v>99.232736572890019</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
-        <v>85</v>
+      <c r="B6">
+        <v>98.976982097186706</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
-        <v>78</v>
+      <c r="B7">
+        <v>98.721227621483379</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
-        <v>76</v>
+      <c r="B8">
+        <v>98.465473145780052</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
-        <v>70</v>
+      <c r="B9">
+        <v>98.209718670076725</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
-        <v>68</v>
+      <c r="B10">
+        <v>97.953964194373398</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
-        <v>65</v>
+      <c r="B11">
+        <v>97.698209718670071</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
-        <v>64</v>
+      <c r="B12">
+        <v>97.442455242966759</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
-        <v>58</v>
+      <c r="B13">
+        <v>97.186700767263432</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
-        <v>61</v>
+      <c r="B14">
+        <v>96.930946291560105</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="3">
-        <v>59</v>
+      <c r="B15">
+        <v>96.675191815856778</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
-        <v>55</v>
+      <c r="B16">
+        <v>96.419437340153451</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3">
-        <v>54</v>
+      <c r="B17">
+        <v>96.163682864450124</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="3">
-        <v>56</v>
+      <c r="B18">
+        <v>95.907928388746797</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="3">
-        <v>74</v>
+      <c r="B19">
+        <v>95.652173913043484</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="3">
-        <v>60</v>
+      <c r="B20">
+        <v>95.396419437340157</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="3">
-        <v>55</v>
+      <c r="B21">
+        <v>95.14066496163683</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="3">
-        <v>54</v>
+      <c r="B22">
+        <v>94.884910485933503</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="3">
-        <v>42</v>
+      <c r="B23">
+        <v>94.629156010230176</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="3">
-        <v>43</v>
+      <c r="B24">
+        <v>94.373401534526849</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="3">
-        <v>45</v>
+      <c r="B25">
+        <v>94.117647058823536</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="3">
-        <v>48</v>
+      <c r="B26">
+        <v>93.861892583120209</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="3">
-        <v>52</v>
+      <c r="B27">
+        <v>93.606138107416882</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="3">
-        <v>38</v>
+      <c r="B28">
+        <v>93.350383631713555</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="3">
-        <v>40</v>
+      <c r="B29">
+        <v>93.094629156010228</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="3">
-        <v>36</v>
+      <c r="B30">
+        <v>92.838874680306901</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="3">
-        <v>35</v>
+      <c r="B31">
+        <v>92.583120204603574</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="3">
-        <v>49</v>
+      <c r="B32">
+        <v>92.327365728900261</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="3">
-        <v>33</v>
+      <c r="B33">
+        <v>92.071611253196934</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="3">
-        <v>31</v>
+      <c r="B34">
+        <v>91.815856777493607</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="3">
-        <v>46</v>
+      <c r="B35">
+        <v>91.56010230179028</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="3">
-        <v>48</v>
+      <c r="B36">
+        <v>91.304347826086953</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="3">
-        <v>34</v>
+      <c r="B37">
+        <v>91.048593350383626</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="3">
-        <v>25</v>
+      <c r="B38">
+        <v>90.792838874680314</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="3">
-        <v>41</v>
+      <c r="B39">
+        <v>90.537084398976987</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="3">
-        <v>30</v>
+      <c r="B40">
+        <v>90.28132992327366</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="3">
-        <v>43</v>
+      <c r="B41">
+        <v>90.025575447570333</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="3">
-        <v>28</v>
+      <c r="B42">
+        <v>89.769820971867006</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="3">
-        <v>27</v>
+      <c r="B43">
+        <v>89.514066496163679</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="3">
-        <v>32</v>
+      <c r="B44">
+        <v>89.258312020460352</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="3">
-        <v>24</v>
+      <c r="B45">
+        <v>89.002557544757039</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="3">
-        <v>39</v>
+      <c r="B46">
+        <v>88.746803069053712</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="3">
-        <v>37</v>
+      <c r="B47">
+        <v>88.491048593350385</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="3">
-        <v>38</v>
+      <c r="B48">
+        <v>88.235294117647058</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="3">
-        <v>22</v>
+      <c r="B49">
+        <v>87.979539641943731</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="3">
-        <v>26</v>
+      <c r="B50">
+        <v>87.723785166240404</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="3">
-        <v>40</v>
+      <c r="B51">
+        <v>87.468030690537091</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="3">
-        <v>29</v>
+      <c r="B52">
+        <v>87.212276214833764</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="3">
-        <v>31</v>
+      <c r="B53">
+        <v>86.956521739130437</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="3">
-        <v>27</v>
+      <c r="B54">
+        <v>86.70076726342711</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="3">
-        <v>28</v>
+      <c r="B55">
+        <v>86.445012787723783</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="3">
-        <v>23</v>
+      <c r="B56">
+        <v>86.189258312020456</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="3">
-        <v>35</v>
+      <c r="B57">
+        <v>85.933503836317129</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="3">
-        <v>34</v>
+      <c r="B58">
+        <v>85.677749360613817</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="3">
-        <v>22</v>
+      <c r="B59">
+        <v>85.42199488491049</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="3">
-        <v>18</v>
+      <c r="B60">
+        <v>85.166240409207163</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="3">
-        <v>21</v>
+      <c r="B61">
+        <v>84.910485933503836</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="3">
-        <v>25</v>
+      <c r="B62">
+        <v>84.654731457800509</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="3">
-        <v>24</v>
+      <c r="B63">
+        <v>84.398976982097182</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="3">
-        <v>31</v>
+      <c r="B64">
+        <v>84.143222506393869</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="3">
-        <v>32</v>
+      <c r="B65">
+        <v>83.887468030690542</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="3">
-        <v>20</v>
+      <c r="B66">
+        <v>83.631713554987215</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="3">
-        <v>19</v>
+      <c r="B67">
+        <v>83.375959079283888</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="3">
-        <v>30</v>
+      <c r="B68">
+        <v>83.120204603580561</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="3">
-        <v>18</v>
+      <c r="B69">
+        <v>82.864450127877234</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="3">
-        <v>22</v>
+      <c r="B70">
+        <v>82.608695652173907</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="3">
-        <v>16</v>
+      <c r="B71">
+        <v>82.352941176470594</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="3">
-        <v>28</v>
+      <c r="B72">
+        <v>82.097186700767267</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="3">
-        <v>15</v>
+      <c r="B73">
+        <v>81.84143222506394</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="3">
-        <v>24</v>
+      <c r="B74">
+        <v>81.585677749360613</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="3">
-        <v>33</v>
+      <c r="B75">
+        <v>81.329923273657286</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="3">
-        <v>28</v>
+      <c r="B76">
+        <v>81.074168797953959</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="3">
-        <v>22</v>
+      <c r="B77">
+        <v>80.818414322250646</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B78" s="3">
-        <v>34</v>
+      <c r="B78">
+        <v>80.562659846547319</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="3">
-        <v>21</v>
+      <c r="B79">
+        <v>80.306905370843992</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B80" s="3">
-        <v>14</v>
+      <c r="B80">
+        <v>80.051150895140665</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="3">
-        <v>21</v>
+      <c r="B81">
+        <v>79.795396419437338</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="3">
-        <v>19</v>
+      <c r="B82">
+        <v>79.539641943734011</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="3">
-        <v>23</v>
+      <c r="B83">
+        <v>79.283887468030684</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="3">
-        <v>18</v>
+      <c r="B84">
+        <v>79.028132992327372</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="3">
-        <v>27</v>
+      <c r="B85">
+        <v>78.772378516624045</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B86" s="3">
-        <v>19</v>
+      <c r="B86">
+        <v>78.516624040920718</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="3">
-        <v>17</v>
+      <c r="B87">
+        <v>78.260869565217391</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="3">
-        <v>15</v>
+      <c r="B88">
+        <v>78.005115089514064</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="3">
-        <v>22</v>
+      <c r="B89">
+        <v>77.749360613810737</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B90" s="3">
-        <v>18</v>
+      <c r="B90">
+        <v>77.493606138107424</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B91" s="3">
-        <v>11</v>
+      <c r="B91">
+        <v>77.237851662404097</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="3">
-        <v>19</v>
+      <c r="B92">
+        <v>76.98209718670077</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B93" s="3">
-        <v>14</v>
+      <c r="B93">
+        <v>76.726342710997443</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="3">
-        <v>18</v>
+      <c r="B94">
+        <v>76.470588235294116</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="3">
-        <v>16</v>
+      <c r="B95">
+        <v>76.214833759590789</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B96" s="3">
-        <v>16</v>
+      <c r="B96">
+        <v>75.959079283887462</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B97" s="3">
-        <v>21</v>
+      <c r="B97">
+        <v>75.703324808184149</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B98" s="3">
-        <v>20</v>
+      <c r="B98">
+        <v>75.447570332480822</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B99" s="3">
-        <v>15</v>
+      <c r="B99">
+        <v>75.191815856777495</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B100" s="3">
-        <v>19</v>
+      <c r="B100">
+        <v>74.936061381074168</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="3">
-        <v>24</v>
+      <c r="B101">
+        <v>74.680306905370841</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B102" s="3">
-        <v>14</v>
+      <c r="B102">
+        <v>74.424552429667514</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B103" s="3">
-        <v>17</v>
+      <c r="B103">
+        <v>74.168797953964187</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B104" s="3">
-        <v>22</v>
+      <c r="B104">
+        <v>73.913043478260875</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B105" s="3">
-        <v>9</v>
+      <c r="B105">
+        <v>73.657289002557548</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B106" s="3">
-        <v>15</v>
+      <c r="B106">
+        <v>73.401534526854221</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B107" s="3">
-        <v>8</v>
+      <c r="B107">
+        <v>73.145780051150894</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B108" s="3">
-        <v>15</v>
+      <c r="B108">
+        <v>72.890025575447567</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B109" s="3">
-        <v>13</v>
+      <c r="B109">
+        <v>72.63427109974424</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B110" s="3">
-        <v>14</v>
+      <c r="B110">
+        <v>72.378516624040927</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B111" s="3">
-        <v>21</v>
+      <c r="B111">
+        <v>72.1227621483376</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B112" s="3">
-        <v>18</v>
+      <c r="B112">
+        <v>71.867007672634273</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B113" s="3">
-        <v>17</v>
+      <c r="B113">
+        <v>71.611253196930946</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B114" s="3">
-        <v>19</v>
+      <c r="B114">
+        <v>71.355498721227619</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B115" s="3">
-        <v>12</v>
+      <c r="B115">
+        <v>71.099744245524292</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B116" s="3">
-        <v>18</v>
+      <c r="B116">
+        <v>70.843989769820965</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B117" s="3">
-        <v>11</v>
+      <c r="B117">
+        <v>70.588235294117652</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B118" s="3">
-        <v>15</v>
+      <c r="B118">
+        <v>70.332480818414325</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B119" s="3">
-        <v>10</v>
+      <c r="B119">
+        <v>70.076726342710998</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B120" s="3">
-        <v>14</v>
+      <c r="B120">
+        <v>69.820971867007671</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B121" s="3">
-        <v>12</v>
+      <c r="B121">
+        <v>69.565217391304344</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B122" s="3">
-        <v>10</v>
+      <c r="B122">
+        <v>69.309462915601017</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B123" s="3">
-        <v>9</v>
+      <c r="B123">
+        <v>69.053708439897704</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B124" s="3">
-        <v>16</v>
+      <c r="B124">
+        <v>68.797953964194377</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B125" s="3">
-        <v>9</v>
+      <c r="B125">
+        <v>68.54219948849105</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B126" s="3">
-        <v>14</v>
+      <c r="B126">
+        <v>68.286445012787723</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B127" s="3">
-        <v>13</v>
+      <c r="B127">
+        <v>68.030690537084396</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B128" s="3">
-        <v>11</v>
+      <c r="B128">
+        <v>67.774936061381069</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B129" s="3">
-        <v>15</v>
+      <c r="B129">
+        <v>67.519181585677742</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="3">
-        <v>12</v>
+      <c r="B130">
+        <v>67.26342710997443</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B131" s="3">
-        <v>8</v>
+      <c r="B131">
+        <v>67.007672634271103</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B132" s="3">
-        <v>14</v>
+      <c r="B132">
+        <v>66.751918158567776</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B133" s="3">
-        <v>4</v>
+      <c r="B133">
+        <v>66.496163682864449</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B134" s="3">
-        <v>14</v>
+      <c r="B134">
+        <v>66.240409207161122</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B135" s="3">
-        <v>15</v>
+      <c r="B135">
+        <v>65.984654731457795</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B136" s="3">
-        <v>12</v>
+      <c r="B136">
+        <v>65.728900255754482</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B137" s="3">
-        <v>11</v>
+      <c r="B137">
+        <v>65.473145780051155</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B138" s="3">
-        <v>9</v>
+      <c r="B138">
+        <v>65.217391304347828</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B139" s="3">
-        <v>10</v>
+      <c r="B139">
+        <v>64.961636828644501</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B140" s="3">
-        <v>16</v>
+      <c r="B140">
+        <v>64.705882352941174</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B141" s="3">
-        <v>8</v>
+      <c r="B141">
+        <v>64.450127877237847</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B142" s="3">
-        <v>14</v>
+      <c r="B142">
+        <v>64.19437340153452</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B143" s="3">
-        <v>13</v>
+      <c r="B143">
+        <v>63.9386189258312</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B144" s="3">
-        <v>11</v>
+      <c r="B144">
+        <v>63.68286445012788</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B145" s="3">
-        <v>11</v>
+      <c r="B145">
+        <v>63.427109974424553</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B146" s="3">
-        <v>14</v>
+      <c r="B146">
+        <v>63.171355498721226</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B147" s="3">
-        <v>13</v>
+      <c r="B147">
+        <v>62.915601023017906</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B148" s="3">
-        <v>16</v>
+      <c r="B148">
+        <v>62.659846547314579</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B149" s="3">
-        <v>14</v>
+      <c r="B149">
+        <v>62.404092071611252</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B150" s="3">
-        <v>1</v>
+      <c r="B150">
+        <v>62.148337595907925</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B151" s="3">
-        <v>13</v>
+      <c r="B151">
+        <v>61.892583120204606</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B152" s="3">
-        <v>6</v>
+      <c r="B152">
+        <v>61.636828644501279</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B153" s="3">
-        <v>7</v>
+      <c r="B153">
+        <v>61.381074168797952</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B154" s="3">
-        <v>16</v>
+      <c r="B154">
+        <v>61.125319693094632</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B155" s="3">
-        <v>11</v>
+      <c r="B155">
+        <v>60.869565217391305</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B156" s="3">
-        <v>11</v>
+      <c r="B156">
+        <v>60.613810741687978</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B157" s="3">
-        <v>4</v>
+      <c r="B157">
+        <v>60.358056265984658</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B158" s="3">
-        <v>15</v>
+      <c r="B158">
+        <v>60.102301790281331</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B159" s="3">
-        <v>6</v>
+      <c r="B159">
+        <v>59.846547314578004</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B160" s="3">
-        <v>10</v>
+      <c r="B160">
+        <v>59.590792838874677</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B161" s="3">
-        <v>9</v>
+      <c r="B161">
+        <v>59.335038363171357</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B162" s="3">
-        <v>11</v>
+      <c r="B162">
+        <v>59.07928388746803</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B163" s="3">
-        <v>9</v>
+      <c r="B163">
+        <v>58.823529411764703</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B164" s="3">
-        <v>4</v>
+      <c r="B164">
+        <v>58.567774936061383</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B165" s="3">
-        <v>7</v>
+      <c r="B165">
+        <v>58.312020460358056</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B166" s="3">
-        <v>7</v>
+      <c r="B166">
+        <v>58.056265984654729</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B167" s="3">
-        <v>5</v>
+      <c r="B167">
+        <v>57.800511508951409</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B168" s="3">
-        <v>9</v>
+      <c r="B168">
+        <v>57.544757033248082</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B169" s="3">
-        <v>8</v>
+      <c r="B169">
+        <v>57.289002557544755</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B170" s="3">
-        <v>12</v>
+      <c r="B170">
+        <v>57.033248081841435</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B171" s="3">
-        <v>4</v>
+      <c r="B171">
+        <v>56.777493606138108</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B172" s="3">
-        <v>6</v>
+      <c r="B172">
+        <v>56.521739130434781</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B173" s="3">
-        <v>6</v>
+      <c r="B173">
+        <v>56.265984654731454</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B174" s="3">
-        <v>16</v>
+      <c r="B174">
+        <v>56.010230179028135</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B175" s="3">
-        <v>10</v>
+      <c r="B175">
+        <v>55.754475703324808</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B176" s="3">
-        <v>6</v>
+      <c r="B176">
+        <v>55.498721227621481</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B177" s="3">
-        <v>9</v>
+      <c r="B177">
+        <v>55.242966751918161</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B178" s="3">
-        <v>9</v>
+      <c r="B178">
+        <v>54.987212276214834</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B179" s="3">
-        <v>9</v>
+      <c r="B179">
+        <v>54.731457800511507</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B180" s="3">
-        <v>9</v>
+      <c r="B180">
+        <v>54.475703324808187</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B181" s="3">
-        <v>8</v>
+      <c r="B181">
+        <v>54.21994884910486</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B182" s="3">
-        <v>7</v>
+      <c r="B182">
+        <v>53.964194373401533</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B183" s="3">
-        <v>11</v>
+      <c r="B183">
+        <v>53.708439897698213</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B184" s="3">
-        <v>8</v>
+      <c r="B184">
+        <v>53.452685421994886</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B185" s="3">
-        <v>7</v>
+      <c r="B185">
+        <v>53.196930946291559</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B186" s="3">
-        <v>5</v>
+      <c r="B186">
+        <v>52.941176470588232</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B187" s="3">
-        <v>5</v>
+      <c r="B187">
+        <v>52.685421994884912</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B188" s="3">
-        <v>11</v>
+      <c r="B188">
+        <v>52.429667519181585</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B189" s="3">
-        <v>8</v>
+      <c r="B189">
+        <v>52.173913043478258</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B190" s="3">
-        <v>8</v>
+      <c r="B190">
+        <v>51.918158567774938</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B191" s="3">
-        <v>4</v>
+      <c r="B191">
+        <v>51.662404092071611</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B192" s="3">
-        <v>6</v>
+      <c r="B192">
+        <v>51.406649616368284</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B193" s="3">
-        <v>9</v>
+      <c r="B193">
+        <v>51.150895140664964</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B194" s="3">
-        <v>5</v>
+      <c r="B194">
+        <v>50.895140664961637</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B195" s="3">
-        <v>7</v>
+      <c r="B195">
+        <v>50.63938618925831</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B196" s="3">
-        <v>8</v>
+      <c r="B196">
+        <v>50.38363171355499</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B197" s="3">
-        <v>5</v>
+      <c r="B197">
+        <v>50.127877237851663</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B198" s="3">
-        <v>9</v>
+      <c r="B198">
+        <v>49.872122762148337</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B199" s="3">
-        <v>7</v>
+      <c r="B199">
+        <v>49.61636828644501</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B200" s="3">
-        <v>8</v>
+      <c r="B200">
+        <v>49.36061381074169</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B201" s="3">
-        <v>9</v>
+      <c r="B201">
+        <v>49.104859335038363</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B202" s="3">
-        <v>7</v>
+      <c r="B202">
+        <v>48.849104859335036</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B203" s="3">
-        <v>8</v>
+      <c r="B203">
+        <v>48.593350383631716</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B204" s="3">
-        <v>8</v>
+      <c r="B204">
+        <v>48.337595907928389</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B205" s="3">
-        <v>10</v>
+      <c r="B205">
+        <v>48.081841432225062</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B206" s="3">
-        <v>4</v>
+      <c r="B206">
+        <v>47.826086956521742</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B207" s="3">
-        <v>4</v>
+      <c r="B207">
+        <v>47.570332480818415</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B208" s="3">
-        <v>4</v>
+      <c r="B208">
+        <v>47.314578005115088</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B209" s="3">
-        <v>6</v>
+      <c r="B209">
+        <v>47.058823529411768</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B210" s="3">
-        <v>7</v>
+      <c r="B210">
+        <v>46.803069053708441</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B211" s="3">
-        <v>11</v>
+      <c r="B211">
+        <v>46.547314578005114</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B212" s="3">
-        <v>3</v>
+      <c r="B212">
+        <v>46.291560102301787</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B213" s="3">
-        <v>3</v>
+      <c r="B213">
+        <v>46.035805626598467</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B214" s="3">
-        <v>6</v>
+      <c r="B214">
+        <v>45.78005115089514</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B215" s="3">
-        <v>7</v>
+      <c r="B215">
+        <v>45.524296675191813</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B216" s="3">
-        <v>6</v>
+      <c r="B216">
+        <v>45.268542199488493</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B217" s="3">
-        <v>3</v>
+      <c r="B217">
+        <v>45.012787723785166</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B218" s="3">
-        <v>4</v>
+      <c r="B218">
+        <v>44.757033248081839</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B219" s="3">
-        <v>12</v>
+      <c r="B219">
+        <v>44.501278772378519</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B220" s="3">
-        <v>4</v>
+      <c r="B220">
+        <v>44.245524296675192</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B221" s="3">
-        <v>2</v>
+      <c r="B221">
+        <v>43.989769820971865</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B222" s="3">
-        <v>5</v>
+      <c r="B222">
+        <v>43.734015345268546</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B223" s="3">
-        <v>2</v>
+      <c r="B223">
+        <v>43.478260869565219</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B224" s="3">
-        <v>5</v>
+      <c r="B224">
+        <v>43.222506393861892</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B225" s="3">
-        <v>4</v>
+      <c r="B225">
+        <v>42.966751918158565</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B226" s="3">
-        <v>7</v>
+      <c r="B226">
+        <v>42.710997442455245</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B227" s="3">
-        <v>5</v>
+      <c r="B227">
+        <v>42.455242966751918</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B228" s="3">
-        <v>5</v>
+      <c r="B228">
+        <v>42.199488491048591</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B229" s="3">
-        <v>4</v>
+      <c r="B229">
+        <v>41.943734015345271</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B230" s="3">
-        <v>5</v>
+      <c r="B230">
+        <v>41.687979539641944</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B231" s="3">
-        <v>7</v>
+      <c r="B231">
+        <v>41.432225063938617</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B232" s="3">
-        <v>6</v>
+      <c r="B232">
+        <v>41.176470588235297</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B233" s="3">
-        <v>6</v>
+      <c r="B233">
+        <v>40.92071611253197</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B234" s="3">
-        <v>6</v>
+      <c r="B234">
+        <v>40.664961636828643</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B235" s="3">
-        <v>6</v>
+      <c r="B235">
+        <v>40.409207161125323</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B236" s="3">
-        <v>6</v>
+      <c r="B236">
+        <v>40.153452685421996</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B237" s="3">
-        <v>6</v>
+      <c r="B237">
+        <v>39.897698209718669</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B238" s="3">
-        <v>6</v>
+      <c r="B238">
+        <v>39.641943734015342</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B239" s="3">
-        <v>6</v>
+      <c r="B239">
+        <v>39.386189258312022</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B240" s="3">
-        <v>6</v>
+      <c r="B240">
+        <v>39.130434782608695</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B241" s="3">
-        <v>6</v>
+      <c r="B241">
+        <v>38.874680306905368</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B242" s="3">
-        <v>5</v>
+      <c r="B242">
+        <v>38.618925831202048</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B243" s="3">
-        <v>2</v>
+      <c r="B243">
+        <v>38.363171355498721</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B244" s="3">
-        <v>6</v>
+      <c r="B244">
+        <v>38.107416879795394</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B245" s="3">
-        <v>2</v>
+      <c r="B245">
+        <v>37.851662404092075</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B246" s="3">
-        <v>2</v>
+      <c r="B246">
+        <v>37.595907928388748</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B247" s="3">
-        <v>5</v>
+      <c r="B247">
+        <v>37.340153452685421</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B248" s="3">
-        <v>4</v>
+      <c r="B248">
+        <v>37.084398976982094</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B249" s="3">
-        <v>5</v>
+      <c r="B249">
+        <v>36.828644501278774</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B250" s="3">
-        <v>4</v>
+      <c r="B250">
+        <v>36.572890025575447</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B251" s="3">
-        <v>3</v>
+      <c r="B251">
+        <v>36.31713554987212</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B252" s="3">
-        <v>6</v>
+      <c r="B252">
+        <v>36.0613810741688</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B253" s="3">
-        <v>3</v>
+      <c r="B253">
+        <v>35.805626598465473</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B254" s="3">
-        <v>4</v>
+      <c r="B254">
+        <v>35.549872122762146</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B255" s="3">
-        <v>3</v>
+      <c r="B255">
+        <v>35.294117647058826</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B256" s="3">
-        <v>6</v>
+      <c r="B256">
+        <v>35.038363171355499</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B257" s="3">
-        <v>2</v>
+      <c r="B257">
+        <v>34.782608695652172</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B258" s="3">
-        <v>3</v>
+      <c r="B258">
+        <v>34.526854219948852</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B259" s="3">
-        <v>4</v>
+      <c r="B259">
+        <v>34.271099744245525</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B260" s="3">
-        <v>2</v>
+      <c r="B260">
+        <v>34.015345268542198</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B261" s="3">
-        <v>1</v>
+      <c r="B261">
+        <v>33.759590792838871</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B262" s="3">
-        <v>5</v>
+      <c r="B262">
+        <v>33.503836317135551</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B263" s="3">
-        <v>5</v>
+      <c r="B263">
+        <v>33.248081841432224</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B264" s="3">
-        <v>5</v>
+      <c r="B264">
+        <v>32.992327365728897</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B265" s="3">
-        <v>5</v>
+      <c r="B265">
+        <v>32.736572890025577</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B266" s="3">
-        <v>5</v>
+      <c r="B266">
+        <v>32.48081841432225</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B267" s="3">
-        <v>5</v>
+      <c r="B267">
+        <v>32.225063938618923</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B268" s="3">
-        <v>5</v>
+      <c r="B268">
+        <v>31.9693094629156</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B269" s="3">
-        <v>5</v>
+      <c r="B269">
+        <v>31.713554987212277</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B270" s="3">
-        <v>4</v>
+      <c r="B270">
+        <v>31.457800511508953</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B271" s="3">
-        <v>5</v>
+      <c r="B271">
+        <v>31.202046035805626</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B272" s="3">
-        <v>5</v>
+      <c r="B272">
+        <v>30.946291560102303</v>
       </c>
     </row>
     <row r="273" spans="1:2" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B273" s="3">
-        <v>5</v>
+      <c r="B273">
+        <v>30.690537084398976</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
